--- a/EECIS_DEVICE_LIST.xlsx
+++ b/EECIS_DEVICE_LIST.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/seung/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/seung/Desktop/sk/ETHZ/EECIS/group_works/eecis-device-rental/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEA0E778-E966-D044-8A00-E1CB97B6A510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7034CAED-3FAE-B44D-AF3E-047B7881BFD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Device List" sheetId="2" r:id="rId1"/>
@@ -218,7 +218,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -268,6 +268,13 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -391,7 +398,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -424,25 +431,28 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -669,17 +679,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="39" customHeight="1">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18"/>
+      <c r="B1" s="16"/>
     </row>
     <row r="2" spans="1:2" ht="1.5" customHeight="1">
-      <c r="A2" s="19"/>
-      <c r="B2" s="12"/>
+      <c r="A2" s="17"/>
+      <c r="B2" s="14"/>
     </row>
     <row r="3" spans="1:2" ht="34.5" customHeight="1">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="12" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
@@ -687,17 +697,17 @@
       </c>
     </row>
     <row r="4" spans="1:2" ht="13">
-      <c r="A4" s="14"/>
-      <c r="B4" s="13" t="s">
+      <c r="A4" s="13"/>
+      <c r="B4" s="12" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15" customHeight="1">
-      <c r="A5" s="12"/>
-      <c r="B5" s="12"/>
+      <c r="A5" s="14"/>
+      <c r="B5" s="14"/>
     </row>
     <row r="6" spans="1:2" ht="20.25" customHeight="1">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="12" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
@@ -705,19 +715,19 @@
       </c>
     </row>
     <row r="7" spans="1:2" ht="15" customHeight="1">
-      <c r="A7" s="14"/>
+      <c r="A7" s="13"/>
       <c r="B7" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="15" customHeight="1">
-      <c r="A8" s="14"/>
+      <c r="A8" s="13"/>
       <c r="B8" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="15" customHeight="1">
-      <c r="A9" s="12"/>
+      <c r="A9" s="14"/>
       <c r="B9" s="4" t="s">
         <v>18</v>
       </c>
@@ -739,7 +749,7 @@
       </c>
     </row>
     <row r="12" spans="1:2" ht="29.25" customHeight="1">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="23" t="s">
         <v>14</v>
       </c>
       <c r="B12" s="5" t="s">
@@ -747,13 +757,13 @@
       </c>
     </row>
     <row r="13" spans="1:2" ht="27.75" customHeight="1">
-      <c r="A13" s="12"/>
+      <c r="A13" s="14"/>
       <c r="B13" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="15" customHeight="1">
-      <c r="A14" s="13" t="s">
+      <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
       <c r="B14" s="5" t="s">
@@ -761,25 +771,25 @@
       </c>
     </row>
     <row r="15" spans="1:2" ht="15" customHeight="1">
-      <c r="A15" s="14"/>
+      <c r="A15" s="13"/>
       <c r="B15" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="15" customHeight="1">
-      <c r="A16" s="14"/>
+      <c r="A16" s="13"/>
       <c r="B16" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="15" customHeight="1">
-      <c r="A17" s="12"/>
+      <c r="A17" s="14"/>
       <c r="B17" s="5" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15" customHeight="1">
-      <c r="A18" s="13" t="s">
+      <c r="A18" s="12" t="s">
         <v>19</v>
       </c>
       <c r="B18" s="5" t="s">
@@ -787,31 +797,31 @@
       </c>
     </row>
     <row r="19" spans="1:2" ht="15" customHeight="1">
-      <c r="A19" s="14"/>
+      <c r="A19" s="13"/>
       <c r="B19" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="15" customHeight="1">
-      <c r="A20" s="14"/>
+      <c r="A20" s="13"/>
       <c r="B20" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="15" customHeight="1">
-      <c r="A21" s="14"/>
+      <c r="A21" s="13"/>
       <c r="B21" s="5" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="15" customHeight="1">
-      <c r="A22" s="14"/>
+      <c r="A22" s="13"/>
       <c r="B22" s="5" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="15" customHeight="1">
-      <c r="A23" s="12"/>
+      <c r="A23" s="14"/>
       <c r="B23" s="5" t="s">
         <v>21</v>
       </c>
@@ -873,7 +883,7 @@
       </c>
     </row>
     <row r="31" spans="1:2" ht="13">
-      <c r="A31" s="15" t="s">
+      <c r="A31" s="18" t="s">
         <v>30</v>
       </c>
       <c r="B31" s="7" t="s">
@@ -881,31 +891,31 @@
       </c>
     </row>
     <row r="32" spans="1:2" ht="13">
-      <c r="A32" s="16"/>
+      <c r="A32" s="19"/>
       <c r="B32" s="7" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="13">
-      <c r="A33" s="16"/>
+      <c r="A33" s="19"/>
       <c r="B33" s="7" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="13">
-      <c r="A34" s="16"/>
+      <c r="A34" s="19"/>
       <c r="B34" s="7" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="13">
-      <c r="A35" s="16"/>
+      <c r="A35" s="19"/>
       <c r="B35" s="7" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="13">
-      <c r="A36" s="16"/>
+      <c r="A36" s="19"/>
       <c r="B36" s="7" t="s">
         <v>21</v>
       </c>
@@ -3504,14 +3514,14 @@
     <row r="780" ht="13"/>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A18:A23"/>
+    <mergeCell ref="A31:A36"/>
     <mergeCell ref="A3:A5"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A6:A9"/>
     <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A18:A23"/>
-    <mergeCell ref="A31:A36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
